--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>136759758</v>
       </c>
       <c r="B3" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 40997-2026 artfynd.xlsx
+++ b/artfynd/A 40997-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858284</v>
       </c>
       <c r="B2" t="n">
-        <v>93485</v>
+        <v>93497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136858285</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>136858279</v>
       </c>
       <c r="B7" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
